--- a/sources/table_normalization/xlsx/employment-table12.xlsx
+++ b/sources/table_normalization/xlsx/employment-table12.xlsx
@@ -1900,10 +1900,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1911,7 +1909,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2218,72 +2222,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="A4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6">
         <v>2023</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
     </row>
     <row r="5" spans="1:10" ht="58" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="5"/>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B7">
@@ -21323,18 +21327,18 @@
       </c>
     </row>
     <row r="608" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A608" s="2" t="s">
+      <c r="A608" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="B608" s="2"/>
-      <c r="C608" s="2"/>
-      <c r="D608" s="2"/>
-      <c r="E608" s="2"/>
-      <c r="F608" s="2"/>
-      <c r="G608" s="2"/>
-      <c r="H608" s="2"/>
-      <c r="I608" s="2"/>
-      <c r="J608" s="2"/>
+      <c r="B608" s="4"/>
+      <c r="C608" s="4"/>
+      <c r="D608" s="4"/>
+      <c r="E608" s="4"/>
+      <c r="F608" s="4"/>
+      <c r="G608" s="4"/>
+      <c r="H608" s="4"/>
+      <c r="I608" s="4"/>
+      <c r="J608" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
